--- a/docs/eu/0.0.1/StructureDefinition-Observation-resultslab-eu-lab.xlsx
+++ b/docs/eu/0.0.1/StructureDefinition-Observation-resultslab-eu-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T14:53:25+02:00</t>
+    <t>2026-03-15T17:07:07+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/eu/0.0.1/StructureDefinition-Observation-resultslab-eu-lab.xlsx
+++ b/docs/eu/0.0.1/StructureDefinition-Observation-resultslab-eu-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T17:07:07+02:00</t>
+    <t>2026-03-15T18:07:36+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
